--- a/output/final/chem/chem distributors (status checked)/status_check_report.xlsx
+++ b/output/final/chem/chem distributors (status checked)/status_check_report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status changes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status changes'!$A$1:$H$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status changes'!$A$1:$H$69</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Status changes'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="24" customHeight="1">
+    <row r="57" ht="33" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
           <t>antioxidants_verified_distributors</t>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Redox Ltd</t>
+          <t>Maha Chemicals Asia Pte Ltd</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>redox.com</t>
+          <t>maha.asia</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -2848,7 +2848,7 @@
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Redox Pty Ltd' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Maha Chemicals (Asia) Pte Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="33" customHeight="1">
+    <row r="58" ht="24" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>antioxidants_verified_distributors</t>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>First Quality Chemicals</t>
+          <t>Redox Ltd</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>firstqualitychemicals.com</t>
+          <t>redox.com</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2882,7 +2882,7 @@
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'First Quality Chemicals, S.A. de C.V.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Redox Pty Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -2899,12 +2899,12 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Jungwoo Co., Ltd.</t>
+          <t>Quimica Iberoamericana S.A. de C.V.</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>https://jungwookorea.tradekorea.com</t>
+          <t>quimibero.com.mx</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -2916,7 +2916,7 @@
       <c r="F59" s="9" t="inlineStr"/>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Asian Chem Corp.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Química Iberoamericana S.A. de C.V.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>PT. Graha Jaya Pratama Kinerja</t>
+          <t>Univar Solutions B.V. (acquired by Apollo Global Management)</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>grahachemical.co.id</t>
+          <t>univarsolutions.com</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -2950,7 +2950,7 @@
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'PT Graha Jaya Pratama Kinerja' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Univar Solutions (acquired by Apollo Funds)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="24" customHeight="1">
+    <row r="61" ht="33" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
           <t>antioxidants_verified_distributors</t>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>PT Rena Haniem Mulia</t>
+          <t>First Quality Chemicals</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>renahaniemmulia.com</t>
+          <t>firstqualitychemicals.com</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
@@ -2984,7 +2984,7 @@
       <c r="F61" s="9" t="inlineStr"/>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'PT. Rena Haniem Mulia' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'First Quality Chemicals, S.A. de C.V.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Simar, S.A.</t>
+          <t>Brenntag SA</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>simarsa.es</t>
+          <t>brenntag.com</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3018,7 +3018,7 @@
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'SIMAR S.A.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Brenntag S.p.A.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>PT. Jebsen Jessen Ingredients Indonesia</t>
+          <t>Jungwoo Co., Ltd.</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>jj-group.com</t>
+          <t>https://jungwookorea.tradekorea.com</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -3052,7 +3052,7 @@
       <c r="F63" s="9" t="inlineStr"/>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'PT Jebsen &amp; Jessen Ingredients Indonesia' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Asian Chem Corp.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
@@ -3061,7 +3061,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="24" customHeight="1">
+    <row r="64" ht="33" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>antioxidants_verified_distributors</t>
@@ -3069,12 +3069,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Chemipol Solutions (Pty) Ltd</t>
+          <t>PT. Graha Jaya Pratama Kinerja</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>chemipol.co.za</t>
+          <t>grahachemical.co.id</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3086,17 +3086,187 @@
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
+          <t>Same company as 'PT Graha Jaya Pratama Kinerja' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>antioxidants_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>PT Rena Haniem Mulia</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>renahaniemmulia.com</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'PT. Rena Haniem Mulia' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>antioxidants_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Simar, S.A.</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>simarsa.es</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'SIMAR S.A.' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="33" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>antioxidants_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>PT. Jebsen Jessen Ingredients Indonesia</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>jj-group.com</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr"/>
+      <c r="F67" s="9" t="inlineStr"/>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'PT Jebsen &amp; Jessen Ingredients Indonesia' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>antioxidants_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Chemipol Solutions (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>chemipol.co.za</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
           <t>Same company as 'Chemipol Solutions' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>duplicate</t>
         </is>
       </c>
     </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>antioxidants_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Disan Mexico</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>disan.com.mx</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr"/>
+      <c r="F69" s="9" t="inlineStr"/>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'Disan México' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H64"/>
+  <autoFilter ref="A1:H69"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -3161,6 +3331,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
